--- a/stories/arbres/TREE-SEC-017.xlsx
+++ b/stories/arbres/TREE-SEC-017.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Maya est à la maison avec Maman. Papa range les chaussures. Plus tard, Maya ira à l'école. La maîtresse sera à l'école. Si Maya cherche, elle va vers Papa. Ou vers Maman. Ou vers la maîtresse. Les pieds vont vers eux. Les mains peuvent tenir la main de Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya voit une pomme. Elle cherche. Elle va vers Papa, ou Maman, ou la maîtresse. Les pieds vont vers eux.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1869,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On va vers qui ? Papa, maman, ou la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2046,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya retient : papa, maman, maîtresse. Les mains peuvent tenir la main de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2195,6 +2237,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2361,6 +2408,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la cuisine. Les chaussures tapent doux. Maya va dans la cuisine. Elle va vers Maman. Papa et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2547,6 +2599,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2713,6 +2770,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend les cubes. Un oiseau chante dehors. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2875,6 +2937,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3041,6 +3108,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend le livre. Le pain sent bon. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3203,6 +3275,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3369,6 +3446,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend la dînette. La porte claque doux. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3531,6 +3613,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3697,6 +3784,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le jardin. L'eau coule. Maya va vers le jardin, près de la porte. Elle va vers Papa. Maman et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3883,6 +3975,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4049,6 +4146,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend les cubes. Le pain sent bon. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4211,6 +4313,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4377,6 +4484,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend le livre. La porte claque doux. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4539,6 +4651,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4705,6 +4822,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend la dînette. Le tapis est chaud. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4867,6 +4989,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5033,6 +5160,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la chambre. Un oiseau chante dehors. Maya va dans la chambre. Elle va vers Maman. Papa et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5219,6 +5351,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5385,6 +5522,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend les cubes. La porte claque doux. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5547,6 +5689,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5713,6 +5860,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend le livre. Le tapis est chaud. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5875,6 +6027,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6041,6 +6198,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend la dînette. Les chaussures tapent doux. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6203,6 +6365,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6369,6 +6536,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Maya voit un yaourt. Elle cherche. Elle va vers Papa, ou Maman, ou la maîtresse. Les pieds vont vers eux.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6553,6 +6725,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On va vers qui ? Papa, maman, ou la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -6725,6 +6902,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya retient : papa, maman, maîtresse. Les mains peuvent tenir la main de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6911,6 +7093,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7077,6 +7264,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la cuisine. Le pain sent bon. Maya va dans la cuisine. Elle va vers Maman. Papa et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7263,6 +7455,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7429,6 +7626,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend les cubes. Le pain sent bon. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7591,6 +7793,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7757,6 +7964,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend le livre. La porte claque doux. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7919,6 +8131,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8085,6 +8302,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend la dînette. Le tapis est chaud. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8247,6 +8469,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8413,6 +8640,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le jardin. La porte claque doux. Maya va vers le jardin, près de la porte. Elle va vers Papa. Maman et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8599,6 +8831,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8765,6 +9002,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend les cubes. La porte claque doux. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8927,6 +9169,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9093,6 +9340,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend le livre. Le tapis est chaud. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9255,6 +9507,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9421,6 +9678,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend la dînette. Les chaussures tapent doux. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9583,6 +9845,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9749,6 +10016,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la chambre. Le tapis est chaud. Maya va dans la chambre. Elle va vers Maman. Papa et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9935,6 +10207,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10101,6 +10378,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend les cubes. Le tapis est chaud. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10263,6 +10545,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10429,6 +10716,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend le livre. Les chaussures tapent doux. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10591,6 +10883,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10757,6 +11054,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend la dînette. L'eau coule. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10919,6 +11221,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11085,6 +11392,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Maya voit un morceau de pain. Elle cherche. Elle va vers Papa, ou Maman, ou la maîtresse. Les pieds vont vers eux.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11269,6 +11581,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On va vers qui ? Papa, maman, ou la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -11441,6 +11758,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya retient : papa, maman, maîtresse. Les mains peuvent tenir la main de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11627,6 +11949,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11793,6 +12120,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la cuisine. Les chaussures tapent doux. Maya va dans la cuisine. Elle va vers Maman. Papa et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11979,6 +12311,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12145,6 +12482,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend les cubes. La porte claque doux. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12307,6 +12649,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12473,6 +12820,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend le livre. Le tapis est chaud. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12635,6 +12987,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12801,6 +13158,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend la dînette. Les chaussures tapent doux. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12963,6 +13325,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13129,6 +13496,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le jardin. L'eau coule. Maya va vers le jardin, près de la porte. Elle va vers Papa. Maman et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13315,6 +13687,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13481,6 +13858,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend les cubes. Le tapis est chaud. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13643,6 +14025,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13809,6 +14196,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend le livre. Les chaussures tapent doux. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13971,6 +14363,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14137,6 +14534,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend la dînette. L'eau coule. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14299,6 +14701,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14465,6 +14872,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la chambre. Un oiseau chante dehors. Maya va dans la chambre. Elle va vers Maman. Papa et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14651,6 +15063,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14817,6 +15234,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend les cubes. Les chaussures tapent doux. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14979,6 +15401,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15145,6 +15572,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend le livre. L'eau coule. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15307,6 +15739,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15473,6 +15910,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Maya prend la dînette. Un oiseau chante dehors. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15635,6 +16077,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15653,7 +16100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15670,6 +16117,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-017.xlsx
+++ b/stories/arbres/TREE-SEC-017.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Maya est à la maison avec Maman. Papa range les chaussures. Plus tard, Maya ira à l'école. La maîtresse sera à l'école. Si Maya cherche, elle va vers Papa. Ou vers Maman. Ou vers la maîtresse. Les pieds vont vers eux. Les mains peuvent tenir la main de Maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Maya voit une pomme. Elle cherche. Elle va vers Papa, ou Maman, ou la maîtresse. Les pieds vont vers eux.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1876,6 +1884,7 @@
           <t>narrateur|On va vers qui ? Papa, maman, ou la maîtresse.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2051,6 +2060,7 @@
           <t>narrateur|Oui. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya retient : papa, maman, maîtresse. Les mains peuvent tenir la main de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2242,6 +2252,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2413,6 +2424,7 @@
           <t>narrateur|Maya a choisi la cuisine. Les chaussures tapent doux. Maya va dans la cuisine. Elle va vers Maman. Papa et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2604,6 +2616,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2775,6 +2788,7 @@
           <t>narrateur|Maya prend les cubes. Un oiseau chante dehors. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2942,6 +2956,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3113,6 +3128,7 @@
           <t>narrateur|Maya prend le livre. Le pain sent bon. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3280,6 +3296,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3451,6 +3468,7 @@
           <t>narrateur|Maya prend la dînette. La porte claque doux. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3618,6 +3636,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3789,6 +3808,7 @@
           <t>narrateur|Maya a choisi le jardin. L'eau coule. Maya va vers le jardin, près de la porte. Elle va vers Papa. Maman et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3980,6 +4000,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4151,6 +4172,7 @@
           <t>narrateur|Maya prend les cubes. Le pain sent bon. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4318,6 +4340,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4489,6 +4512,7 @@
           <t>narrateur|Maya prend le livre. La porte claque doux. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4656,6 +4680,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4827,6 +4852,7 @@
           <t>narrateur|Maya prend la dînette. Le tapis est chaud. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4994,6 +5020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5165,6 +5192,7 @@
           <t>narrateur|Maya a choisi la chambre. Un oiseau chante dehors. Maya va dans la chambre. Elle va vers Maman. Papa et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5356,6 +5384,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5527,6 +5556,7 @@
           <t>narrateur|Maya prend les cubes. La porte claque doux. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5694,6 +5724,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5865,6 +5896,7 @@
           <t>narrateur|Maya prend le livre. Le tapis est chaud. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6032,6 +6064,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6203,6 +6236,7 @@
           <t>narrateur|Maya prend la dînette. Les chaussures tapent doux. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6370,6 +6404,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6541,6 +6576,7 @@
           <t>narrateur|Maya voit un yaourt. Elle cherche. Elle va vers Papa, ou Maman, ou la maîtresse. Les pieds vont vers eux.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6732,6 +6768,7 @@
           <t>narrateur|On va vers qui ? Papa, maman, ou la maîtresse.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6907,6 +6944,7 @@
           <t>narrateur|Oui. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya retient : papa, maman, maîtresse. Les mains peuvent tenir la main de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7098,6 +7136,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7269,6 +7308,7 @@
           <t>narrateur|Maya a choisi la cuisine. Le pain sent bon. Maya va dans la cuisine. Elle va vers Maman. Papa et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7460,6 +7500,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7631,6 +7672,7 @@
           <t>narrateur|Maya prend les cubes. Le pain sent bon. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7798,6 +7840,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7969,6 +8012,7 @@
           <t>narrateur|Maya prend le livre. La porte claque doux. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8136,6 +8180,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8307,6 +8352,7 @@
           <t>narrateur|Maya prend la dînette. Le tapis est chaud. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8474,6 +8520,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8645,6 +8692,7 @@
           <t>narrateur|Maya a choisi le jardin. La porte claque doux. Maya va vers le jardin, près de la porte. Elle va vers Papa. Maman et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8836,6 +8884,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9007,6 +9056,7 @@
           <t>narrateur|Maya prend les cubes. La porte claque doux. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9174,6 +9224,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9345,6 +9396,7 @@
           <t>narrateur|Maya prend le livre. Le tapis est chaud. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9512,6 +9564,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9683,6 +9736,7 @@
           <t>narrateur|Maya prend la dînette. Les chaussures tapent doux. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9850,6 +9904,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10021,6 +10076,7 @@
           <t>narrateur|Maya a choisi la chambre. Le tapis est chaud. Maya va dans la chambre. Elle va vers Maman. Papa et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10212,6 +10268,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10383,6 +10440,7 @@
           <t>narrateur|Maya prend les cubes. Le tapis est chaud. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10550,6 +10608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10721,6 +10780,7 @@
           <t>narrateur|Maya prend le livre. Les chaussures tapent doux. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10888,6 +10948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11059,6 +11120,7 @@
           <t>narrateur|Maya prend la dînette. L'eau coule. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11226,6 +11288,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11397,6 +11460,7 @@
           <t>narrateur|Maya voit un morceau de pain. Elle cherche. Elle va vers Papa, ou Maman, ou la maîtresse. Les pieds vont vers eux.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11588,6 +11652,7 @@
           <t>narrateur|On va vers qui ? Papa, maman, ou la maîtresse.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11763,6 +11828,7 @@
           <t>narrateur|Oui. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya retient : papa, maman, maîtresse. Les mains peuvent tenir la main de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11954,6 +12020,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12125,6 +12192,7 @@
           <t>narrateur|Maya a choisi la cuisine. Les chaussures tapent doux. Maya va dans la cuisine. Elle va vers Maman. Papa et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12316,6 +12384,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12487,6 +12556,7 @@
           <t>narrateur|Maya prend les cubes. La porte claque doux. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12654,6 +12724,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12825,6 +12896,7 @@
           <t>narrateur|Maya prend le livre. Le tapis est chaud. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12992,6 +13064,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13163,6 +13236,7 @@
           <t>narrateur|Maya prend la dînette. Les chaussures tapent doux. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13330,6 +13404,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13501,6 +13576,7 @@
           <t>narrateur|Maya a choisi le jardin. L'eau coule. Maya va vers le jardin, près de la porte. Elle va vers Papa. Maman et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13692,6 +13768,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13863,6 +13940,7 @@
           <t>narrateur|Maya prend les cubes. Le tapis est chaud. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14030,6 +14108,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14201,6 +14280,7 @@
           <t>narrateur|Maya prend le livre. Les chaussures tapent doux. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14368,6 +14448,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14539,6 +14620,7 @@
           <t>narrateur|Maya prend la dînette. L'eau coule. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14706,6 +14788,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14877,6 +14960,7 @@
           <t>narrateur|Maya a choisi la chambre. Un oiseau chante dehors. Maya va dans la chambre. Elle va vers Maman. Papa et la maîtresse sont des adultes connus. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15068,6 +15152,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15239,6 +15324,7 @@
           <t>narrateur|Maya prend les cubes. Les chaussures tapent doux. Maya range les cubes. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15406,6 +15492,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15577,6 +15664,7 @@
           <t>narrateur|Maya prend le livre. L'eau coule. Maya range le livre. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15744,6 +15832,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15915,6 +16004,7 @@
           <t>narrateur|Maya prend la dînette. Un oiseau chante dehors. Maya range la dînette. Elle va vers Papa, Maman, ou la maîtresse. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Maya dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16082,6 +16172,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16100,7 +16191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16124,6 +16215,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16325,6 +16430,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
